--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/1.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/1.xlsx
@@ -426,13 +426,13 @@
         <v>-13.8489365825129</v>
       </c>
       <c r="E2">
-        <v>-14.19331286508632</v>
+        <v>-29.94467909935908</v>
       </c>
       <c r="F2">
-        <v>-0.3336913881172326</v>
+        <v>-3.655473666202348</v>
       </c>
       <c r="G2">
-        <v>-10.71968002865001</v>
+        <v>-17.93035443864504</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.91599399510932</v>
       </c>
       <c r="E3">
-        <v>-14.79987478756972</v>
+        <v>-29.39017877830486</v>
       </c>
       <c r="F3">
-        <v>-0.1204952980261266</v>
+        <v>-3.664178150870965</v>
       </c>
       <c r="G3">
-        <v>-10.04385202008103</v>
+        <v>-17.84004110106095</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.84067800273087</v>
       </c>
       <c r="E4">
-        <v>-15.82782933036287</v>
+        <v>-29.83099175939652</v>
       </c>
       <c r="F4">
-        <v>-0.2495342301972196</v>
+        <v>-3.731465606632967</v>
       </c>
       <c r="G4">
-        <v>-10.81403719761032</v>
+        <v>-17.7083989129646</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.58625972384976</v>
       </c>
       <c r="E5">
-        <v>-15.1647248814197</v>
+        <v>-30.75054821986807</v>
       </c>
       <c r="F5">
-        <v>0.09443290830423309</v>
+        <v>-3.561695020898819</v>
       </c>
       <c r="G5">
-        <v>-10.77547596316889</v>
+        <v>-17.50165699930988</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.1715431675541</v>
       </c>
       <c r="E6">
-        <v>-16.59124853552396</v>
+        <v>-30.4476997278941</v>
       </c>
       <c r="F6">
-        <v>0.0138236479704104</v>
+        <v>-3.733380792068239</v>
       </c>
       <c r="G6">
-        <v>-10.67251137580647</v>
+        <v>-17.47343294331483</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.61911210597058</v>
       </c>
       <c r="E7">
-        <v>-16.62916091991617</v>
+        <v>-31.50438970250293</v>
       </c>
       <c r="F7">
-        <v>0.6519415661037592</v>
+        <v>-3.746483907645721</v>
       </c>
       <c r="G7">
-        <v>-9.873173534258365</v>
+        <v>-17.47385007205278</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.94002335506085</v>
       </c>
       <c r="E8">
-        <v>-17.54408927995189</v>
+        <v>-31.10510509229862</v>
       </c>
       <c r="F8">
-        <v>0.3883890215964713</v>
+        <v>-3.3748890595261</v>
       </c>
       <c r="G8">
-        <v>-10.01457686587726</v>
+        <v>-17.07650349897452</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.17084715203751</v>
       </c>
       <c r="E9">
-        <v>-17.97043605082603</v>
+        <v>-32.20094825317776</v>
       </c>
       <c r="F9">
-        <v>0.374379672080326</v>
+        <v>-3.477549460122445</v>
       </c>
       <c r="G9">
-        <v>-9.516170924394439</v>
+        <v>-17.00180600469918</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.32471537490314</v>
       </c>
       <c r="E10">
-        <v>-18.94908004014967</v>
+        <v>-31.9886058427211</v>
       </c>
       <c r="F10">
-        <v>0.7663034846320506</v>
+        <v>-3.392935043396087</v>
       </c>
       <c r="G10">
-        <v>-8.663251903293229</v>
+        <v>-16.74608456979094</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.422341643194793</v>
       </c>
       <c r="E11">
-        <v>-18.31394797515188</v>
+        <v>-32.66407755417922</v>
       </c>
       <c r="F11">
-        <v>0.7091809252698021</v>
+        <v>-3.435774891999266</v>
       </c>
       <c r="G11">
-        <v>-8.343019522733988</v>
+        <v>-16.41479993294885</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.483057522001396</v>
       </c>
       <c r="E12">
-        <v>-20.62790762359128</v>
+        <v>-33.39560045266727</v>
       </c>
       <c r="F12">
-        <v>0.7548637307993893</v>
+        <v>-3.320622710968704</v>
       </c>
       <c r="G12">
-        <v>-8.407578471295315</v>
+        <v>-16.31578979223309</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.509349931490444</v>
       </c>
       <c r="E13">
-        <v>-20.77301351621906</v>
+        <v>-33.52105729657578</v>
       </c>
       <c r="F13">
-        <v>0.5917987791909038</v>
+        <v>-3.285632471874453</v>
       </c>
       <c r="G13">
-        <v>-7.814894813945133</v>
+        <v>-15.99516676730022</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.524440882676569</v>
       </c>
       <c r="E14">
-        <v>-21.83351873017935</v>
+        <v>-33.80788857598461</v>
       </c>
       <c r="F14">
-        <v>0.8213783197745784</v>
+        <v>-3.342161091808894</v>
       </c>
       <c r="G14">
-        <v>-6.856223726137444</v>
+        <v>-15.81148445859929</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.531804842305315</v>
       </c>
       <c r="E15">
-        <v>-22.67600509151436</v>
+        <v>-34.96971160315552</v>
       </c>
       <c r="F15">
-        <v>1.083541692147372</v>
+        <v>-2.913049381443291</v>
       </c>
       <c r="G15">
-        <v>-6.612233209347618</v>
+        <v>-15.08931874411714</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.54611705824905</v>
       </c>
       <c r="E16">
-        <v>-23.56849486284206</v>
+        <v>-35.00375214227117</v>
       </c>
       <c r="F16">
-        <v>1.454202970204038</v>
+        <v>-2.961001085289146</v>
       </c>
       <c r="G16">
-        <v>-6.402241995246108</v>
+        <v>-14.94319954037756</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.580094075866515</v>
       </c>
       <c r="E17">
-        <v>-23.55347844303263</v>
+        <v>-35.99920809134828</v>
       </c>
       <c r="F17">
-        <v>1.529024427494501</v>
+        <v>-3.015568131213758</v>
       </c>
       <c r="G17">
-        <v>-4.652754410108395</v>
+        <v>-14.77003317958213</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.639737096558045</v>
       </c>
       <c r="E18">
-        <v>-24.57727131821273</v>
+        <v>-36.36836929245357</v>
       </c>
       <c r="F18">
-        <v>1.600403189858929</v>
+        <v>-2.839410004436624</v>
       </c>
       <c r="G18">
-        <v>-4.729413402615759</v>
+        <v>-14.26050380508736</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.742351907193842</v>
       </c>
       <c r="E19">
-        <v>-25.51376427147297</v>
+        <v>-37.0900133248939</v>
       </c>
       <c r="F19">
-        <v>1.711783814104545</v>
+        <v>-2.703360598935638</v>
       </c>
       <c r="G19">
-        <v>-4.042998269412193</v>
+        <v>-14.21238502567405</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.8904285969856361</v>
       </c>
       <c r="E20">
-        <v>-27.1130809082879</v>
+        <v>-38.08673271821915</v>
       </c>
       <c r="F20">
-        <v>1.82106038514705</v>
+        <v>-2.472849973391217</v>
       </c>
       <c r="G20">
-        <v>-4.252264474040603</v>
+        <v>-13.98955220542571</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.08982797898995472</v>
       </c>
       <c r="E21">
-        <v>-26.99976037471996</v>
+        <v>-37.8414592447787</v>
       </c>
       <c r="F21">
-        <v>1.739139819214595</v>
+        <v>-2.513131823454552</v>
       </c>
       <c r="G21">
-        <v>-3.915572061060105</v>
+        <v>-13.8590637424498</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.6593601195069949</v>
       </c>
       <c r="E22">
-        <v>-28.52585158683086</v>
+        <v>-38.7261532481022</v>
       </c>
       <c r="F22">
-        <v>1.973029355395036</v>
+        <v>-2.284959679088233</v>
       </c>
       <c r="G22">
-        <v>-2.835632379603373</v>
+        <v>-13.77002827544387</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.359837359269001</v>
       </c>
       <c r="E23">
-        <v>-28.09893875670576</v>
+        <v>-39.38717912747585</v>
       </c>
       <c r="F23">
-        <v>1.891503092346314</v>
+        <v>-2.362091453065104</v>
       </c>
       <c r="G23">
-        <v>-3.510890974339596</v>
+        <v>-13.4699455303094</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.010450308720282</v>
       </c>
       <c r="E24">
-        <v>-28.4372565213448</v>
+        <v>-39.36143701697925</v>
       </c>
       <c r="F24">
-        <v>2.166433263131053</v>
+        <v>-2.020350137774973</v>
       </c>
       <c r="G24">
-        <v>-2.874233340591275</v>
+        <v>-13.20582358609527</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.612715499399115</v>
       </c>
       <c r="E25">
-        <v>-28.39033700215133</v>
+        <v>-39.40497150185198</v>
       </c>
       <c r="F25">
-        <v>1.954387775362436</v>
+        <v>-1.962846529407437</v>
       </c>
       <c r="G25">
-        <v>-2.446825358743668</v>
+        <v>-13.95160838772735</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.165689257028488</v>
       </c>
       <c r="E26">
-        <v>-29.93817621068407</v>
+        <v>-39.30445296430373</v>
       </c>
       <c r="F26">
-        <v>2.298788150015552</v>
+        <v>-2.022174202795938</v>
       </c>
       <c r="G26">
-        <v>-2.425985474573956</v>
+        <v>-13.52726597104911</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.666767380150178</v>
       </c>
       <c r="E27">
-        <v>-29.07393279597921</v>
+        <v>-39.67048498986971</v>
       </c>
       <c r="F27">
-        <v>2.317653389246908</v>
+        <v>-2.07975650606674</v>
       </c>
       <c r="G27">
-        <v>-2.673740081641933</v>
+        <v>-13.61925113413053</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.110145587308526</v>
       </c>
       <c r="E28">
-        <v>-29.12789862072862</v>
+        <v>-39.70962911919202</v>
       </c>
       <c r="F28">
-        <v>2.317931720694249</v>
+        <v>-2.032078163463809</v>
       </c>
       <c r="G28">
-        <v>-2.522732857413617</v>
+        <v>-13.97210231988821</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.485965877348834</v>
       </c>
       <c r="E29">
-        <v>-29.08867750734818</v>
+        <v>-39.64365830984827</v>
       </c>
       <c r="F29">
-        <v>2.176032384594694</v>
+        <v>-2.0813130084166</v>
       </c>
       <c r="G29">
-        <v>-2.310023685424365</v>
+        <v>-13.52692664013134</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.780889653339691</v>
       </c>
       <c r="E30">
-        <v>-28.56120085493474</v>
+        <v>-39.44904487513163</v>
       </c>
       <c r="F30">
-        <v>2.16789118975998</v>
+        <v>-1.877537940797533</v>
       </c>
       <c r="G30">
-        <v>-2.502737162356419</v>
+        <v>-13.53931304626652</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.981121879331185</v>
       </c>
       <c r="E31">
-        <v>-28.44196160583877</v>
+        <v>-39.62914455065369</v>
       </c>
       <c r="F31">
-        <v>2.171814337779639</v>
+        <v>-1.993596355766758</v>
       </c>
       <c r="G31">
-        <v>-2.487955576523574</v>
+        <v>-13.63959112592381</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.07258696374693</v>
       </c>
       <c r="E32">
-        <v>-27.53211872211367</v>
+        <v>-39.20610809427914</v>
       </c>
       <c r="F32">
-        <v>2.367355433414879</v>
+        <v>-1.987782044966508</v>
       </c>
       <c r="G32">
-        <v>-3.054896431760382</v>
+        <v>-13.84130101035884</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.043130227123818</v>
       </c>
       <c r="E33">
-        <v>-27.92485063042889</v>
+        <v>-38.47108694962017</v>
       </c>
       <c r="F33">
-        <v>2.121958217274748</v>
+        <v>-2.014245070016341</v>
       </c>
       <c r="G33">
-        <v>-3.030126930035555</v>
+        <v>-13.63410555196524</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.884396032425408</v>
       </c>
       <c r="E34">
-        <v>-28.3700132108049</v>
+        <v>-38.46602411567959</v>
       </c>
       <c r="F34">
-        <v>2.384389980686048</v>
+        <v>-1.896863752304845</v>
       </c>
       <c r="G34">
-        <v>-3.353140168847784</v>
+        <v>-14.33342188113535</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.593405033242822</v>
       </c>
       <c r="E35">
-        <v>-26.85731722480869</v>
+        <v>-38.19195181178736</v>
       </c>
       <c r="F35">
-        <v>2.131835670185729</v>
+        <v>-1.891134763347084</v>
       </c>
       <c r="G35">
-        <v>-3.831189565809622</v>
+        <v>-14.41467756612399</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.17301936966303</v>
       </c>
       <c r="E36">
-        <v>-27.15729240002479</v>
+        <v>-37.96893805233162</v>
       </c>
       <c r="F36">
-        <v>2.28641896795695</v>
+        <v>-2.001483241808812</v>
       </c>
       <c r="G36">
-        <v>-3.58059451066895</v>
+        <v>-14.47203442286463</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.632350200588462</v>
       </c>
       <c r="E37">
-        <v>-26.06863819163282</v>
+        <v>-37.72566163592856</v>
       </c>
       <c r="F37">
-        <v>2.730099175835588</v>
+        <v>-1.72012825344796</v>
       </c>
       <c r="G37">
-        <v>-4.131542120405539</v>
+        <v>-14.28821141597829</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.983589913033284</v>
       </c>
       <c r="E38">
-        <v>-25.85762941677141</v>
+        <v>-36.95540443501589</v>
       </c>
       <c r="F38">
-        <v>2.647192852693802</v>
+        <v>-2.042733453366019</v>
       </c>
       <c r="G38">
-        <v>-3.950541353591427</v>
+        <v>-14.44458337925299</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.241176973310922</v>
       </c>
       <c r="E39">
-        <v>-25.13610312465529</v>
+        <v>-36.70204310699775</v>
       </c>
       <c r="F39">
-        <v>2.751083378883305</v>
+        <v>-1.806821043987942</v>
       </c>
       <c r="G39">
-        <v>-4.847047017262682</v>
+        <v>-14.54660446113671</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.423531457448634</v>
       </c>
       <c r="E40">
-        <v>-25.7051828677772</v>
+        <v>-36.18951268304662</v>
       </c>
       <c r="F40">
-        <v>2.530888412605946</v>
+        <v>-1.822566651580355</v>
       </c>
       <c r="G40">
-        <v>-4.417887756824801</v>
+        <v>-14.13576575971316</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.549140278561453</v>
       </c>
       <c r="E41">
-        <v>-25.24117277858126</v>
+        <v>-35.93121984683413</v>
       </c>
       <c r="F41">
-        <v>3.038462254997315</v>
+        <v>-1.779819580126289</v>
       </c>
       <c r="G41">
-        <v>-4.449884179461857</v>
+        <v>-14.27174310719318</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.3604613978816866</v>
       </c>
       <c r="E42">
-        <v>-22.87794786141241</v>
+        <v>-35.28294388602907</v>
       </c>
       <c r="F42">
-        <v>3.070215234281426</v>
+        <v>-1.720139022224196</v>
       </c>
       <c r="G42">
-        <v>-4.490491331046558</v>
+        <v>-14.42909002612921</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.284921611456213</v>
       </c>
       <c r="E43">
-        <v>-22.88820032656577</v>
+        <v>-34.60463055713114</v>
       </c>
       <c r="F43">
-        <v>2.963382347077179</v>
+        <v>-1.657660239235446</v>
       </c>
       <c r="G43">
-        <v>-4.550918718774875</v>
+        <v>-14.87424253206731</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.205271752955393</v>
       </c>
       <c r="E44">
-        <v>-22.42373286149506</v>
+        <v>-34.31156583325074</v>
       </c>
       <c r="F44">
-        <v>2.607416306746176</v>
+        <v>-1.688608045404036</v>
       </c>
       <c r="G44">
-        <v>-5.343807617612481</v>
+        <v>-14.46889933623894</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.101538362678744</v>
       </c>
       <c r="E45">
-        <v>-22.91251823198697</v>
+        <v>-34.00045061197577</v>
       </c>
       <c r="F45">
-        <v>3.136292445267937</v>
+        <v>-1.5531650048419</v>
       </c>
       <c r="G45">
-        <v>-5.025276857460425</v>
+        <v>-14.65262468203188</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.958769544810076</v>
       </c>
       <c r="E46">
-        <v>-21.70006912964731</v>
+        <v>-33.91410166959751</v>
       </c>
       <c r="F46">
-        <v>2.747466726802683</v>
+        <v>-1.561405603764949</v>
       </c>
       <c r="G46">
-        <v>-6.260752589443197</v>
+        <v>-14.71540752291138</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.760706523606455</v>
       </c>
       <c r="E47">
-        <v>-20.03059737350555</v>
+        <v>-33.05238740762594</v>
       </c>
       <c r="F47">
-        <v>3.128754301902462</v>
+        <v>-1.809051009036278</v>
       </c>
       <c r="G47">
-        <v>-5.043239877556511</v>
+        <v>-15.13896037447851</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.498391720341469</v>
       </c>
       <c r="E48">
-        <v>-20.28192315245725</v>
+        <v>-32.41488921495914</v>
       </c>
       <c r="F48">
-        <v>3.140490611265325</v>
+        <v>-1.617274014879359</v>
       </c>
       <c r="G48">
-        <v>-5.222860146880747</v>
+        <v>-14.82276685947718</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.166003486898233</v>
       </c>
       <c r="E49">
-        <v>-19.30482337277023</v>
+        <v>-32.13843719797588</v>
       </c>
       <c r="F49">
-        <v>2.902797211971229</v>
+        <v>-1.592287140541315</v>
       </c>
       <c r="G49">
-        <v>-5.224614736016561</v>
+        <v>-14.5443268058057</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.756947396094033</v>
       </c>
       <c r="E50">
-        <v>-18.70399902685455</v>
+        <v>-32.2542846200401</v>
       </c>
       <c r="F50">
-        <v>3.116800960280064</v>
+        <v>-1.465160908703286</v>
       </c>
       <c r="G50">
-        <v>-5.371900907058736</v>
+        <v>-14.79255316561302</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.276331462199654</v>
       </c>
       <c r="E51">
-        <v>-18.57274120774222</v>
+        <v>-31.32892718436473</v>
       </c>
       <c r="F51">
-        <v>3.205814007915288</v>
+        <v>-1.63553123243706</v>
       </c>
       <c r="G51">
-        <v>-5.597948267025712</v>
+        <v>-15.04264998365003</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.721610650337659</v>
       </c>
       <c r="E52">
-        <v>-18.29203921790277</v>
+        <v>-31.3829881070683</v>
       </c>
       <c r="F52">
-        <v>3.044081899457907</v>
+        <v>-1.612650068036932</v>
       </c>
       <c r="G52">
-        <v>-5.667711393174773</v>
+        <v>-15.48598996590538</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.103948001189453</v>
       </c>
       <c r="E53">
-        <v>-17.99173799255811</v>
+        <v>-30.6393968253498</v>
       </c>
       <c r="F53">
-        <v>3.267229167158844</v>
+        <v>-1.443499101120079</v>
       </c>
       <c r="G53">
-        <v>-5.685823387820126</v>
+        <v>-15.0291595105775</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.43209945152782</v>
       </c>
       <c r="E54">
-        <v>-16.93022745736812</v>
+        <v>-29.91407114354124</v>
       </c>
       <c r="F54">
-        <v>3.316521997829831</v>
+        <v>-1.539460494529985</v>
       </c>
       <c r="G54">
-        <v>-6.700558564335374</v>
+        <v>-14.99455603332827</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.7103486688786</v>
       </c>
       <c r="E55">
-        <v>-16.22261263740356</v>
+        <v>-29.73061813301651</v>
       </c>
       <c r="F55">
-        <v>3.220245824806861</v>
+        <v>-1.630923852942689</v>
       </c>
       <c r="G55">
-        <v>-6.118955302905133</v>
+        <v>-15.25180031918457</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.955733998642287</v>
       </c>
       <c r="E56">
-        <v>-14.87429572941177</v>
+        <v>-29.97151257209153</v>
       </c>
       <c r="F56">
-        <v>3.016394547386736</v>
+        <v>-1.336004348360995</v>
       </c>
       <c r="G56">
-        <v>-6.100906208625027</v>
+        <v>-15.28293599998141</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.165004479656906</v>
       </c>
       <c r="E57">
-        <v>-15.53328832395598</v>
+        <v>-29.30923230541776</v>
       </c>
       <c r="F57">
-        <v>3.114998432811573</v>
+        <v>-1.551828019853781</v>
       </c>
       <c r="G57">
-        <v>-6.118501758166253</v>
+        <v>-15.31440273533219</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.351670954241481</v>
       </c>
       <c r="E58">
-        <v>-14.25461028925415</v>
+        <v>-28.89543846449287</v>
       </c>
       <c r="F58">
-        <v>3.043160754905994</v>
+        <v>-1.586063616244082</v>
       </c>
       <c r="G58">
-        <v>-6.763041800843578</v>
+        <v>-15.54244138844103</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.515815738810591</v>
       </c>
       <c r="E59">
-        <v>-13.3104370440769</v>
+        <v>-28.61057480704037</v>
       </c>
       <c r="F59">
-        <v>3.151819363866011</v>
+        <v>-1.647308960170063</v>
       </c>
       <c r="G59">
-        <v>-6.379207219383859</v>
+        <v>-15.26759824249797</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.651581478943635</v>
       </c>
       <c r="E60">
-        <v>-14.61745426911873</v>
+        <v>-28.10005276131164</v>
       </c>
       <c r="F60">
-        <v>3.054565717307737</v>
+        <v>-1.594506336813414</v>
       </c>
       <c r="G60">
-        <v>-7.212537742529202</v>
+        <v>-15.71009569091357</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.763182732816048</v>
       </c>
       <c r="E61">
-        <v>-13.78104059142801</v>
+        <v>-28.35683987991659</v>
       </c>
       <c r="F61">
-        <v>2.971283315365081</v>
+        <v>-1.640648886251555</v>
       </c>
       <c r="G61">
-        <v>-6.587798072722258</v>
+        <v>-15.30546922819446</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.83218892865489</v>
       </c>
       <c r="E62">
-        <v>-12.65975872781078</v>
+        <v>-28.10842590975183</v>
       </c>
       <c r="F62">
-        <v>2.709742875279193</v>
+        <v>-1.760424185757141</v>
       </c>
       <c r="G62">
-        <v>-6.482516103482356</v>
+        <v>-15.4856671877153</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.861502846150398</v>
       </c>
       <c r="E63">
-        <v>-12.89333741712641</v>
+        <v>-27.87548120679726</v>
       </c>
       <c r="F63">
-        <v>2.509327665845881</v>
+        <v>-1.730831588659532</v>
       </c>
       <c r="G63">
-        <v>-6.753444529325231</v>
+        <v>-15.35122427809273</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.838797468338361</v>
       </c>
       <c r="E64">
-        <v>-12.73745375636038</v>
+        <v>-27.86374340216938</v>
       </c>
       <c r="F64">
-        <v>2.394467898508507</v>
+        <v>-1.69158022764528</v>
       </c>
       <c r="G64">
-        <v>-6.528648555572099</v>
+        <v>-15.50206100922577</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.753946355313492</v>
       </c>
       <c r="E65">
-        <v>-11.69275744516086</v>
+        <v>-27.91662239315695</v>
       </c>
       <c r="F65">
-        <v>2.42455585931299</v>
+        <v>-1.707320865033276</v>
       </c>
       <c r="G65">
-        <v>-6.172029968990729</v>
+        <v>-15.54793358349068</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.60669628763798</v>
       </c>
       <c r="E66">
-        <v>-12.82655148246129</v>
+        <v>-27.20161710361187</v>
       </c>
       <c r="F66">
-        <v>2.174928999214165</v>
+        <v>-1.958709662597856</v>
       </c>
       <c r="G66">
-        <v>-5.961949370159657</v>
+        <v>-15.74688247294596</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.381083774992318</v>
       </c>
       <c r="E67">
-        <v>-12.1209835327482</v>
+        <v>-27.88866359463359</v>
       </c>
       <c r="F67">
-        <v>2.364018769516403</v>
+        <v>-2.127187166816234</v>
       </c>
       <c r="G67">
-        <v>-6.942251562520945</v>
+        <v>-15.97167017033524</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.082853268313102</v>
       </c>
       <c r="E68">
-        <v>-10.96063452386679</v>
+        <v>-27.53440107301354</v>
       </c>
       <c r="F68">
-        <v>2.14052358750629</v>
+        <v>-2.169250006795587</v>
       </c>
       <c r="G68">
-        <v>-6.69921117230089</v>
+        <v>-15.36255627547365</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.70623762707206</v>
       </c>
       <c r="E69">
-        <v>-11.23014665443329</v>
+        <v>-27.42010238905994</v>
       </c>
       <c r="F69">
-        <v>1.916572803424638</v>
+        <v>-2.232406394319827</v>
       </c>
       <c r="G69">
-        <v>-6.603066308749376</v>
+        <v>-15.65828730849675</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.252723500602642</v>
       </c>
       <c r="E70">
-        <v>-12.33945523277425</v>
+        <v>-27.409510288356</v>
       </c>
       <c r="F70">
-        <v>2.040301072176384</v>
+        <v>-2.340307047106282</v>
       </c>
       <c r="G70">
-        <v>-5.969245812528211</v>
+        <v>-15.27892527406058</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.731528452597851</v>
       </c>
       <c r="E71">
-        <v>-10.94110774394571</v>
+        <v>-27.20204278016859</v>
       </c>
       <c r="F71">
-        <v>1.944863206965047</v>
+        <v>-2.432317956372237</v>
       </c>
       <c r="G71">
-        <v>-6.126086217996723</v>
+        <v>-15.01595374442135</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.142366944357992</v>
       </c>
       <c r="E72">
-        <v>-11.60706513151372</v>
+        <v>-27.46085865512897</v>
       </c>
       <c r="F72">
-        <v>1.467740150300588</v>
+        <v>-2.297570744428453</v>
       </c>
       <c r="G72">
-        <v>-6.325013588905989</v>
+        <v>-15.33729350246348</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.501676143630464</v>
       </c>
       <c r="E73">
-        <v>-11.57530241482392</v>
+        <v>-27.10033325395631</v>
       </c>
       <c r="F73">
-        <v>1.615196174938122</v>
+        <v>-2.517800502136729</v>
       </c>
       <c r="G73">
-        <v>-5.7291849132935</v>
+        <v>-15.36414202678696</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.815053442593884</v>
       </c>
       <c r="E74">
-        <v>-11.41292039385687</v>
+        <v>-27.19570744503186</v>
       </c>
       <c r="F74">
-        <v>1.414527485079553</v>
+        <v>-2.579447604253069</v>
       </c>
       <c r="G74">
-        <v>-5.168693000767192</v>
+        <v>-15.11209033160901</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.092579308567356</v>
       </c>
       <c r="E75">
-        <v>-12.25850423141313</v>
+        <v>-27.39868723547767</v>
       </c>
       <c r="F75">
-        <v>1.210798806035043</v>
+        <v>-2.478761203177594</v>
       </c>
       <c r="G75">
-        <v>-5.08085429597371</v>
+        <v>-14.88346405666695</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.344534811257327</v>
       </c>
       <c r="E76">
-        <v>-11.67382389533479</v>
+        <v>-27.423679883526</v>
       </c>
       <c r="F76">
-        <v>1.238274096051097</v>
+        <v>-2.813390155947288</v>
       </c>
       <c r="G76">
-        <v>-5.167805774562668</v>
+        <v>-14.72861163379477</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.573352530824687</v>
       </c>
       <c r="E77">
-        <v>-12.27483390868479</v>
+        <v>-27.56350557546084</v>
       </c>
       <c r="F77">
-        <v>1.28955997869322</v>
+        <v>-2.837474109816281</v>
       </c>
       <c r="G77">
-        <v>-5.032109823453481</v>
+        <v>-14.7707979156017</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.792407199157618</v>
       </c>
       <c r="E78">
-        <v>-12.70424192798812</v>
+        <v>-28.16154038138779</v>
       </c>
       <c r="F78">
-        <v>0.9599658429977413</v>
+        <v>-2.766507874418447</v>
       </c>
       <c r="G78">
-        <v>-4.440962259233522</v>
+        <v>-14.39739155259069</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.006825530523572</v>
       </c>
       <c r="E79">
-        <v>-13.0553299893288</v>
+        <v>-28.23135586516404</v>
       </c>
       <c r="F79">
-        <v>1.00593029344428</v>
+        <v>-3.06183824923193</v>
       </c>
       <c r="G79">
-        <v>-3.949385973198221</v>
+        <v>-14.72245236381895</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.22624448877217</v>
       </c>
       <c r="E80">
-        <v>-13.43345304049526</v>
+        <v>-28.2960949295777</v>
       </c>
       <c r="F80">
-        <v>1.204748410524995</v>
+        <v>-2.929671401747866</v>
       </c>
       <c r="G80">
-        <v>-4.003116127300593</v>
+        <v>-14.40935751944238</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.4601737599185288</v>
       </c>
       <c r="E81">
-        <v>-14.04649068080963</v>
+        <v>-29.29687862832483</v>
       </c>
       <c r="F81">
-        <v>1.249642610287117</v>
+        <v>-2.962267659048027</v>
       </c>
       <c r="G81">
-        <v>-3.59490599903522</v>
+        <v>-14.05545854602152</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.2850847416905415</v>
       </c>
       <c r="E82">
-        <v>-14.5844915068169</v>
+        <v>-29.00511357648464</v>
       </c>
       <c r="F82">
-        <v>1.142284538149496</v>
+        <v>-3.074788116839895</v>
       </c>
       <c r="G82">
-        <v>-3.746178066906677</v>
+        <v>-14.22893113227933</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.9986193286238054</v>
       </c>
       <c r="E83">
-        <v>-15.4338792625396</v>
+        <v>-29.76351070397122</v>
       </c>
       <c r="F83">
-        <v>1.001599588662444</v>
+        <v>-3.08778851485943</v>
       </c>
       <c r="G83">
-        <v>-2.931131686774729</v>
+        <v>-14.34005290385051</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.675271863450632</v>
       </c>
       <c r="E84">
-        <v>-16.9346427195256</v>
+        <v>-30.4231418133505</v>
       </c>
       <c r="F84">
-        <v>0.9528435400684712</v>
+        <v>-3.00999984553214</v>
       </c>
       <c r="G84">
-        <v>-2.580568087984685</v>
+        <v>-14.04184889330958</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.315833193867714</v>
       </c>
       <c r="E85">
-        <v>-17.1245669194073</v>
+        <v>-30.89677490981275</v>
       </c>
       <c r="F85">
-        <v>0.7302562487318273</v>
+        <v>-3.148183125462737</v>
       </c>
       <c r="G85">
-        <v>-2.269373496747654</v>
+        <v>-13.91986522182405</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.924713489033279</v>
       </c>
       <c r="E86">
-        <v>-19.25391879645001</v>
+        <v>-31.84473395926041</v>
       </c>
       <c r="F86">
-        <v>0.8485338599731518</v>
+        <v>-3.334052203302889</v>
       </c>
       <c r="G86">
-        <v>-2.372569822297816</v>
+        <v>-14.14658296726273</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.50454258261275</v>
       </c>
       <c r="E87">
-        <v>-19.86629980803326</v>
+        <v>-32.23756775824079</v>
       </c>
       <c r="F87">
-        <v>0.8108878749855255</v>
+        <v>-3.348257875893498</v>
       </c>
       <c r="G87">
-        <v>-1.727245180327683</v>
+        <v>-13.92896756678428</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.055527723766458</v>
       </c>
       <c r="E88">
-        <v>-21.06922552953478</v>
+        <v>-33.03154963447965</v>
       </c>
       <c r="F88">
-        <v>0.7111888878541882</v>
+        <v>-3.223686329125703</v>
       </c>
       <c r="G88">
-        <v>-1.839893113392464</v>
+        <v>-13.84832598799317</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.57078235964579</v>
       </c>
       <c r="E89">
-        <v>-21.75062954194295</v>
+        <v>-34.15330472363068</v>
       </c>
       <c r="F89">
-        <v>0.531939293929806</v>
+        <v>-3.279995431698402</v>
       </c>
       <c r="G89">
-        <v>-1.417215901120476</v>
+        <v>-13.79231486801424</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.043211247766333</v>
       </c>
       <c r="E90">
-        <v>-24.47322962788651</v>
+        <v>-35.17978524813434</v>
       </c>
       <c r="F90">
-        <v>0.9002289561122577</v>
+        <v>-3.431572584164864</v>
       </c>
       <c r="G90">
-        <v>-1.716333622230245</v>
+        <v>-14.08446885658215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.459601775471092</v>
       </c>
       <c r="E91">
-        <v>-25.38941237522234</v>
+        <v>-36.20445211879792</v>
       </c>
       <c r="F91">
-        <v>0.4658032688576962</v>
+        <v>-3.448768663079579</v>
       </c>
       <c r="G91">
-        <v>-1.858518242596404</v>
+        <v>-13.52191778473042</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.803509882924623</v>
       </c>
       <c r="E92">
-        <v>-27.39052692531584</v>
+        <v>-37.83116828759626</v>
       </c>
       <c r="F92">
-        <v>0.2379541877784698</v>
+        <v>-3.798620523610519</v>
       </c>
       <c r="G92">
-        <v>-1.508153276538716</v>
+        <v>-13.9430473169628</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>6.060304507525064</v>
       </c>
       <c r="E93">
-        <v>-28.74156997466025</v>
+        <v>-38.58188285892883</v>
       </c>
       <c r="F93">
-        <v>0.5043024722702061</v>
+        <v>-3.725319120504194</v>
       </c>
       <c r="G93">
-        <v>-2.108997428643201</v>
+        <v>-14.17976290993007</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>6.210129991461388</v>
       </c>
       <c r="E94">
-        <v>-31.16258274864098</v>
+        <v>-39.47638100847894</v>
       </c>
       <c r="F94">
-        <v>0.3827693771358794</v>
+        <v>-3.747303991374493</v>
       </c>
       <c r="G94">
-        <v>-1.866850885718749</v>
+        <v>-13.90235409119408</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>6.244743163126855</v>
       </c>
       <c r="E95">
-        <v>-32.57655120855896</v>
+        <v>-41.13939968915977</v>
       </c>
       <c r="F95">
-        <v>0.1574120252042739</v>
+        <v>-3.830133276347818</v>
       </c>
       <c r="G95">
-        <v>-2.471581618286338</v>
+        <v>-13.95630108602927</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>6.143375447543185</v>
       </c>
       <c r="E96">
-        <v>-34.7849136358505</v>
+        <v>-43.25591107815373</v>
       </c>
       <c r="F96">
-        <v>-0.1812154570187332</v>
+        <v>-4.109645975604844</v>
       </c>
       <c r="G96">
-        <v>-2.157427399337199</v>
+        <v>-13.95882041118466</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>5.911170651553759</v>
       </c>
       <c r="E97">
-        <v>-36.26055085480495</v>
+        <v>-44.29604495179051</v>
       </c>
       <c r="F97">
-        <v>0.2111051435189323</v>
+        <v>-4.15569823299608</v>
       </c>
       <c r="G97">
-        <v>-2.306961430800539</v>
+        <v>-14.78103908822743</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>5.523723605355725</v>
       </c>
       <c r="E98">
-        <v>-39.11336721083907</v>
+        <v>-45.62645174508197</v>
       </c>
       <c r="F98">
-        <v>-0.2765829110008319</v>
+        <v>-4.027273121070461</v>
       </c>
       <c r="G98">
-        <v>-3.288395829736257</v>
+        <v>-14.72256161182175</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>5.016385382999627</v>
       </c>
       <c r="E99">
-        <v>-41.63267504163029</v>
+        <v>-47.08814352832979</v>
       </c>
       <c r="F99">
-        <v>-0.3084493766191261</v>
+        <v>-4.334523702810229</v>
       </c>
       <c r="G99">
-        <v>-3.212336045971502</v>
+        <v>-14.72725099957813</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.340353116143212</v>
       </c>
       <c r="E100">
-        <v>-43.7149760737333</v>
+        <v>-48.73422118774793</v>
       </c>
       <c r="F100">
-        <v>-0.3362253640023963</v>
+        <v>-4.406412739494781</v>
       </c>
       <c r="G100">
-        <v>-2.850609287623036</v>
+        <v>-15.23652546206637</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.602150654269682</v>
       </c>
       <c r="E101">
-        <v>-46.0219686649119</v>
+        <v>-50.67126688758091</v>
       </c>
       <c r="F101">
-        <v>-0.4147902135861098</v>
+        <v>-4.571759014930576</v>
       </c>
       <c r="G101">
-        <v>-3.660150230523176</v>
+        <v>-15.47395447759736</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.650935963675226</v>
       </c>
       <c r="E102">
-        <v>-47.98925098569409</v>
+        <v>-52.50573812266614</v>
       </c>
       <c r="F102">
-        <v>-0.259601379243442</v>
+        <v>-4.616086611389184</v>
       </c>
       <c r="G102">
-        <v>-4.062692704825317</v>
+        <v>-15.32750587457662</v>
       </c>
     </row>
   </sheetData>
